--- a/outputs/daily/hr_rankings_2026-10-24.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-24.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
         <v>36.5</v>
@@ -811,7 +811,7 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -826,12 +826,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.6</v>
+        <v>47.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>46.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
         <v>28.5</v>
@@ -2191,13 +2191,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2253,22 +2253,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2283,67 +2283,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,11 +2454,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>28.5</v>
@@ -2473,7 +2473,7 @@
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2529,22 +2529,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2554,72 +2554,72 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
         <v>28.5</v>
@@ -3019,13 +3019,13 @@
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -3091,87 +3091,87 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.1</v>
+        <v>42.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,11 +3282,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
@@ -3295,13 +3295,13 @@
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3387,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>36.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3571,7 +3571,7 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.5</v>
+        <v>32.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,11 +3834,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q13" t="n">
         <v>36.5</v>
@@ -3847,13 +3847,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3862,12 +3862,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3909,27 +3909,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3939,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.8</v>
+        <v>32.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,11 +4110,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
@@ -4123,13 +4123,13 @@
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4185,27 +4185,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4215,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4323,24 +4323,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -4353,17 +4353,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>28.7</v>
+        <v>32.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4390,22 +4390,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4414,12 +4414,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,112 +4476,112 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>29.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,26 +4662,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>26.9</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>24.9</v>
+        <v>5.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4767,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4875,24 +4875,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
@@ -4954,10 +4954,10 @@
         <v>40.2</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>27</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,112 +5028,112 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -5151,24 +5151,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5181,17 +5181,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.9</v>
+        <v>28.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5218,22 +5218,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5242,24 +5242,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,112 +5304,112 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -5427,24 +5427,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5457,17 +5457,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5494,22 +5494,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5580,112 +5580,112 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
         <v>36.5</v>
@@ -6105,7 +6105,7 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6120,12 +6120,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.6</v>
+        <v>47.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>46.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
         <v>28.5</v>
@@ -7485,13 +7485,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7547,22 +7547,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7577,67 +7577,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,11 +7748,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>28.5</v>
@@ -7767,7 +7767,7 @@
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -7823,22 +7823,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7848,72 +7848,72 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,11 +8300,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
         <v>28.5</v>
@@ -8313,13 +8313,13 @@
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -8385,87 +8385,87 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.1</v>
+        <v>42.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,11 +8576,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
@@ -8589,13 +8589,13 @@
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8681,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>36.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8865,7 +8865,7 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.5</v>
+        <v>32.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,11 +9128,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q13" t="n">
         <v>36.5</v>
@@ -9141,13 +9141,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -9156,12 +9156,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9203,27 +9203,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9233,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.8</v>
+        <v>32.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,11 +9404,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
@@ -9417,13 +9417,13 @@
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9479,27 +9479,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9509,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9617,24 +9617,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -9647,17 +9647,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>28.7</v>
+        <v>32.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9684,22 +9684,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9708,12 +9708,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,112 +9770,112 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>29.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,26 +9956,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>26.9</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>24.9</v>
+        <v>5.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9984,12 +9984,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10061,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10169,24 +10169,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -10204,12 +10204,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
@@ -10248,10 +10248,10 @@
         <v>40.2</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>27</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,112 +10322,112 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -10445,24 +10445,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -10475,17 +10475,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10494,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.9</v>
+        <v>28.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10512,22 +10512,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -10536,24 +10536,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10583,12 +10583,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,112 +10598,112 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -10721,24 +10721,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -10751,17 +10751,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10788,22 +10788,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -10874,112 +10874,112 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
